--- a/Data_Set_Depression_Categorized.xlsx
+++ b/Data_Set_Depression_Categorized.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10913"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/prapatsornch./Documents/Reserch/Chat Bot โรคซึมเศร้า/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/prapatsornch./Documents/Reserch/ChatBOt/workaw_chatbot/workaw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E0FAD5-5CE8-3343-9967-1BEFAF48335C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC642FF-3C75-324E-801F-D274119E7830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="700" windowWidth="34200" windowHeight="19700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2241,13 +2241,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C301"/>
+  <dimension ref="A1:D301"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="67.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="174.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="169.5" customWidth="1"/>
     <col min="3" max="3" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.83203125" hidden="1"/>
+    <col min="5" max="16384" width="8.83203125" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">

--- a/Data_Set_Depression_Categorized.xlsx
+++ b/Data_Set_Depression_Categorized.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/prapatsornch./Documents/Reserch/ChatBOt/workaw_chatbot/workaw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC642FF-3C75-324E-801F-D274119E7830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF8B9D7-B697-0F46-9436-CE862632553A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="34200" windowHeight="19700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="700" windowWidth="34200" windowHeight="19840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Question" sheetId="1" r:id="rId1"/>
+    <sheet name="2Q9Q" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$C$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Question!$C$1:$C$302</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="677">
   <si>
     <t>Question</t>
   </si>
@@ -1832,6 +1833,228 @@
   </si>
   <si>
     <t>การป้องกันและการช่วยเหลือ</t>
+  </si>
+  <si>
+    <t>variable</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>allowed_values</t>
+  </si>
+  <si>
+    <t>description_th</t>
+  </si>
+  <si>
+    <t>respondent_id</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>เช่น R001</t>
+  </si>
+  <si>
+    <t>รหัสผู้ตอบ (ไม่ใช่ข้อมูลระบุตัวตนจริง)</t>
+  </si>
+  <si>
+    <t>date_iso</t>
+  </si>
+  <si>
+    <t>date(YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>เช่น 2025-08-26</t>
+  </si>
+  <si>
+    <t>วันที่เก็บข้อมูล</t>
+  </si>
+  <si>
+    <t>2Q_1_sad_hopeless</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>0=ไม่มี, 1=มี</t>
+  </si>
+  <si>
+    <t>ใน 2 สัปดาห์ที่ผ่านมา รู้สึกเศร้า/หดหู่/ท้อแท้สิ้นหวัง หรือไม่</t>
+  </si>
+  <si>
+    <t>2Q_2_loss_of_interest</t>
+  </si>
+  <si>
+    <t>ใน 2 สัปดาห์ที่ผ่านมา เบื่อ/ทำอะไรไม่เพลิดเพลิน หรือไม่</t>
+  </si>
+  <si>
+    <t>score_2q</t>
+  </si>
+  <si>
+    <t>ผลรวม 0-2</t>
+  </si>
+  <si>
+    <t>คะแนนรวม 2Q (ใช้คัดกรองเบื้องต้น)</t>
+  </si>
+  <si>
+    <t>screen_positive_2q</t>
+  </si>
+  <si>
+    <t>0/1</t>
+  </si>
+  <si>
+    <t>ผลคัดกรองเบื้องต้น (&gt;=1 ให้ทำ 9Q ต่อ)</t>
+  </si>
+  <si>
+    <t>9Q_1_little_interest</t>
+  </si>
+  <si>
+    <t>0=ไม่เลย, 1=บางวัน(1-7วัน), 2=บ่อย(&gt;7วัน), 3=ทุกวัน</t>
+  </si>
+  <si>
+    <t>9Q ข้อ 1: เบื่อ/ไม่สนใจอยากทำอะไร (ช่วง 2 สัปดาห์ที่ผ่านมา)</t>
+  </si>
+  <si>
+    <t>9Q_2_down_depressed</t>
+  </si>
+  <si>
+    <t>9Q ข้อ 2: ไม่สบายใจ ซึมเศร้า ท้อแท้ (ช่วง 2 สัปดาห์ที่ผ่านมา)</t>
+  </si>
+  <si>
+    <t>9Q_3_sleep_problems</t>
+  </si>
+  <si>
+    <t>9Q ข้อ 3: หลับยาก/หลับๆตื่นๆ/หลับมากไป (ช่วง 2 สัปดาห์ที่ผ่านมา)</t>
+  </si>
+  <si>
+    <t>9Q_4_low_energy</t>
+  </si>
+  <si>
+    <t>9Q ข้อ 4: เหนื่อยง่าย หรือไม่ค่อยมีแรง (ช่วง 2 สัปดาห์ที่ผ่านมา)</t>
+  </si>
+  <si>
+    <t>9Q_5_appetite_change</t>
+  </si>
+  <si>
+    <t>9Q ข้อ 5: เบื่ออาหาร หรือกินมากเกินไป (ช่วง 2 สัปดาห์ที่ผ่านมา)</t>
+  </si>
+  <si>
+    <t>9Q_6_feel_bad_about_self</t>
+  </si>
+  <si>
+    <t>9Q ข้อ 6: รู้สึกไม่ดีกับตัวเอง/ล้มเหลว/ทำให้ครอบครัวผิดหวัง (ช่วง 2 สัปดาห์ที่ผ่านมา)</t>
+  </si>
+  <si>
+    <t>9Q_7_concentration</t>
+  </si>
+  <si>
+    <t>9Q ข้อ 7: สมาธิไม่ดี ทำงาน/อ่าน/ดู/ฟัง ไม่ต่อเนื่อง (ช่วง 2 สัปดาห์ที่ผ่านมา)</t>
+  </si>
+  <si>
+    <t>9Q_8_psychomotor_change</t>
+  </si>
+  <si>
+    <t>9Q ข้อ 8: ช้าลงจนคนอื่นสังเกต หรือกระสับกระส่าย (ช่วง 2 สัปดาห์ที่ผ่านมา)</t>
+  </si>
+  <si>
+    <t>9Q_9_suicidal_thoughts</t>
+  </si>
+  <si>
+    <t>9Q ข้อ 9: คิดทำร้ายตนเอง/คิดว่าตายไปจะดีกว่า (ช่วง 2 สัปดาห์ที่ผ่านมา)</t>
+  </si>
+  <si>
+    <t>score_9q</t>
+  </si>
+  <si>
+    <t>ผลรวม 0-27</t>
+  </si>
+  <si>
+    <t>คะแนนรวม 9Q</t>
+  </si>
+  <si>
+    <t>severity_9q</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>none/minimal, mild, moderate, severe</t>
+  </si>
+  <si>
+    <t>ระดับภาวะซึมเศร้าตามเกณฑ์คะแนนรวม 9Q (&lt;7, 7-12, 13-18, ≥19)</t>
+  </si>
+  <si>
+    <t>8Q_1_wish_to_be_dead</t>
+  </si>
+  <si>
+    <t>8Q ข้อ 1: คิดอยากตาย/คิดว่าตายไปจะดีกว่า (ใช้ถ่วงน้ำหนักตามเกณฑ์ทางการ)</t>
+  </si>
+  <si>
+    <t>8Q_2_self_harm_idea</t>
+  </si>
+  <si>
+    <t>8Q ข้อ 2: อยากทำร้ายตัวเอง/ทำให้ตัวเองบาดเจ็บ (ใช้ถ่วงน้ำหนักตามเกณฑ์ทางการ)</t>
+  </si>
+  <si>
+    <t>8Q_3_suicide_idea</t>
+  </si>
+  <si>
+    <t>8Q ข้อ 3: คิดเกี่ยวกับการฆ่าตัวตาย (ใช้ถ่วงน้ำหนักตามเกณฑ์ทางการ)</t>
+  </si>
+  <si>
+    <t>8Q_4_have_plan</t>
+  </si>
+  <si>
+    <t>8Q ข้อ 4: มีแผนการที่จะฆ่าตัวตาย (ใช้ถ่วงน้ำหนักตามเกณฑ์ทางการ)</t>
+  </si>
+  <si>
+    <t>8Q_5_prepare_action</t>
+  </si>
+  <si>
+    <t>8Q ข้อ 5: ได้เตรียมการที่จะทำร้ายตนเอง/เตรียมการจะฆ่าตัวตาย (ใช้ถ่วงน้ำหนักตามเกณฑ์ทางการ)</t>
+  </si>
+  <si>
+    <t>8Q_6_nonfatal_self_injury</t>
+  </si>
+  <si>
+    <t>8Q ข้อ 6: ได้ทำให้ตนเองบาดเจ็บแต่ไม่ถึงทำให้เสียชีวิต (ใช้ถ่วงน้ำหนักตามเกณฑ์ทางการ)</t>
+  </si>
+  <si>
+    <t>8Q_7_attempt_expect_death</t>
+  </si>
+  <si>
+    <t>8Q ข้อ 7: ได้พยายามฆ่าตัวตายโดยคาดหวังว่าจะตายจริง (ใช้ถ่วงน้ำหนักตามเกณฑ์ทางการ)</t>
+  </si>
+  <si>
+    <t>8Q_8_past_attempt_lifetime</t>
+  </si>
+  <si>
+    <t>8Q ข้อ 8: ตลอดชีวิตที่ผ่านมา เคยพยายามฆ่าตัวตาย (ใช้ถ่วงน้ำหนักตามเกณฑ์ทางการ)</t>
+  </si>
+  <si>
+    <t>score_8q_weighted</t>
+  </si>
+  <si>
+    <t>ตามเกณฑ์ไทย (ถ่วงน้ำหนักแต่ละข้อ)</t>
+  </si>
+  <si>
+    <t>คะแนนรวมแบบถ่วงน้ำหนักของ 8Q (ให้กรอกตามเกณฑ์ราชวิทยาลัยจิตแพทย์ฯ)</t>
+  </si>
+  <si>
+    <t>risk_8q_band</t>
+  </si>
+  <si>
+    <t>none, low(1-8), moderate(9-16), high(&gt;=17)</t>
+  </si>
+  <si>
+    <t>ระดับความเสี่ยงการฆ่าตัวตายจาก 8Q (แปลผลจากคะแนนถ่วงน้ำหนัก)</t>
+  </si>
+  <si>
+    <t>กิจกรรมบำบัดภาวะซึมเศร้า ได้แก่ การออกกำลังกาย เช่น เดิน โยคะ การทำสมาธิ การเข้าร่วมกิจกรรมที่สร้างความสุข เช่น ฟังเพลง ดูหนัง ศิลปะ และการทำสวน การสร้างกิจวัตรประจำวันที่ดีควบคู่กับการรับประทานอาหารที่มีประโยชน์ การนอนหลับพักผ่อนให้เพียงพอ การใช้เวลากับคนที่รัก และการหลีกเลี่ยงเครื่องดื่มแอลกอฮอล์</t>
+  </si>
+  <si>
+    <t>มีกิจกรรมแนะนำสำหรับคนไม่ค่อยมีเวลามั้ย?</t>
   </si>
 </sst>
 </file>
@@ -1926,7 +2149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1937,6 +2160,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2241,12 +2467,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D301"/>
+  <dimension ref="A1:D302"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="67.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="169.5" customWidth="1"/>
     <col min="3" max="3" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="0" hidden="1" customWidth="1"/>
     <col min="5" max="16384" width="8.83203125" hidden="1"/>
   </cols>
   <sheetData>
@@ -3020,23 +3247,23 @@
         <v>600</v>
       </c>
     </row>
-    <row r="71" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>597</v>
+    <row r="71" spans="1:3" s="4" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A71" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="72" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>399</v>
+        <v>299</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>597</v>
@@ -3044,10 +3271,10 @@
     </row>
     <row r="73" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>597</v>
@@ -3055,10 +3282,10 @@
     </row>
     <row r="74" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>597</v>
@@ -3066,10 +3293,10 @@
     </row>
     <row r="75" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>597</v>
@@ -3077,10 +3304,10 @@
     </row>
     <row r="76" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>597</v>
@@ -3088,10 +3315,10 @@
     </row>
     <row r="77" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>597</v>
@@ -3099,10 +3326,10 @@
     </row>
     <row r="78" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>597</v>
@@ -3110,32 +3337,32 @@
     </row>
     <row r="79" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="80" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>598</v>
+    <row r="80" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="81" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>598</v>
@@ -3143,10 +3370,10 @@
     </row>
     <row r="82" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>598</v>
@@ -3154,10 +3381,10 @@
     </row>
     <row r="83" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>598</v>
@@ -3165,10 +3392,10 @@
     </row>
     <row r="84" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>598</v>
@@ -3176,10 +3403,10 @@
     </row>
     <row r="85" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>598</v>
@@ -3187,10 +3414,10 @@
     </row>
     <row r="86" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>598</v>
@@ -3198,10 +3425,10 @@
     </row>
     <row r="87" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>598</v>
@@ -3209,10 +3436,10 @@
     </row>
     <row r="88" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>598</v>
@@ -3220,10 +3447,10 @@
     </row>
     <row r="89" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>598</v>
@@ -3231,10 +3458,10 @@
     </row>
     <row r="90" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>598</v>
@@ -3242,10 +3469,10 @@
     </row>
     <row r="91" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>598</v>
@@ -3253,10 +3480,10 @@
     </row>
     <row r="92" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>598</v>
@@ -3264,10 +3491,10 @@
     </row>
     <row r="93" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>598</v>
@@ -3275,10 +3502,10 @@
     </row>
     <row r="94" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>598</v>
@@ -3286,10 +3513,10 @@
     </row>
     <row r="95" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>598</v>
@@ -3297,10 +3524,10 @@
     </row>
     <row r="96" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A96" s="6" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>437</v>
+        <v>414</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>598</v>
@@ -3308,10 +3535,10 @@
     </row>
     <row r="97" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="6" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>598</v>
@@ -3319,10 +3546,10 @@
     </row>
     <row r="98" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A98" s="6" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>598</v>
@@ -3330,10 +3557,10 @@
     </row>
     <row r="99" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A99" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>598</v>
@@ -3341,10 +3568,10 @@
     </row>
     <row r="100" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A100" s="6" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>475</v>
+        <v>454</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>598</v>
@@ -3352,10 +3579,10 @@
     </row>
     <row r="101" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A101" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>598</v>
@@ -3363,10 +3590,10 @@
     </row>
     <row r="102" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A102" s="6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>598</v>
@@ -3374,10 +3601,10 @@
     </row>
     <row r="103" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A103" s="6" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>598</v>
@@ -3385,10 +3612,10 @@
     </row>
     <row r="104" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>598</v>
@@ -3396,10 +3623,10 @@
     </row>
     <row r="105" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A105" s="6" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>598</v>
@@ -3407,10 +3634,10 @@
     </row>
     <row r="106" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A106" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>598</v>
@@ -3418,10 +3645,10 @@
     </row>
     <row r="107" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A107" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>598</v>
@@ -3429,10 +3656,10 @@
     </row>
     <row r="108" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A108" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>598</v>
@@ -3440,10 +3667,10 @@
     </row>
     <row r="109" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A109" s="6" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>526</v>
+        <v>510</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>598</v>
@@ -3451,10 +3678,10 @@
     </row>
     <row r="110" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A110" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>598</v>
@@ -3462,10 +3689,10 @@
     </row>
     <row r="111" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A111" s="6" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>598</v>
@@ -3473,10 +3700,10 @@
     </row>
     <row r="112" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A112" s="6" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>598</v>
@@ -3484,10 +3711,10 @@
     </row>
     <row r="113" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A113" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>598</v>
@@ -3495,10 +3722,10 @@
     </row>
     <row r="114" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A114" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>598</v>
@@ -3506,10 +3733,10 @@
     </row>
     <row r="115" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A115" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>598</v>
@@ -3517,10 +3744,10 @@
     </row>
     <row r="116" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A116" s="6" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>598</v>
@@ -3528,10 +3755,10 @@
     </row>
     <row r="117" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" s="6" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>598</v>
@@ -3539,10 +3766,10 @@
     </row>
     <row r="118" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A118" s="6" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>598</v>
@@ -3550,10 +3777,10 @@
     </row>
     <row r="119" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A119" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>598</v>
@@ -3561,10 +3788,10 @@
     </row>
     <row r="120" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A120" s="6" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>598</v>
@@ -3572,10 +3799,10 @@
     </row>
     <row r="121" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A121" s="6" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>598</v>
@@ -3583,10 +3810,10 @@
     </row>
     <row r="122" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A122" s="6" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>598</v>
@@ -3594,32 +3821,32 @@
     </row>
     <row r="123" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A123" s="6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="124" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B124" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="C124" s="7" t="s">
-        <v>601</v>
+    <row r="124" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="125" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A125" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C125" s="7" t="s">
         <v>601</v>
@@ -3627,10 +3854,10 @@
     </row>
     <row r="126" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A126" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C126" s="7" t="s">
         <v>601</v>
@@ -3638,10 +3865,10 @@
     </row>
     <row r="127" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A127" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C127" s="7" t="s">
         <v>601</v>
@@ -3649,10 +3876,10 @@
     </row>
     <row r="128" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A128" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C128" s="7" t="s">
         <v>601</v>
@@ -3660,10 +3887,10 @@
     </row>
     <row r="129" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A129" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C129" s="7" t="s">
         <v>601</v>
@@ -3671,10 +3898,10 @@
     </row>
     <row r="130" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A130" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>601</v>
@@ -3682,10 +3909,10 @@
     </row>
     <row r="131" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A131" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>601</v>
@@ -3693,10 +3920,10 @@
     </row>
     <row r="132" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A132" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>601</v>
@@ -3704,10 +3931,10 @@
     </row>
     <row r="133" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A133" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>601</v>
@@ -3715,10 +3942,10 @@
     </row>
     <row r="134" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A134" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>601</v>
@@ -3726,10 +3953,10 @@
     </row>
     <row r="135" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A135" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>601</v>
@@ -3737,10 +3964,10 @@
     </row>
     <row r="136" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A136" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>601</v>
@@ -3748,10 +3975,10 @@
     </row>
     <row r="137" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A137" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C137" s="7" t="s">
         <v>601</v>
@@ -3759,10 +3986,10 @@
     </row>
     <row r="138" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A138" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C138" s="7" t="s">
         <v>601</v>
@@ -3770,10 +3997,10 @@
     </row>
     <row r="139" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A139" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C139" s="7" t="s">
         <v>601</v>
@@ -3781,10 +4008,10 @@
     </row>
     <row r="140" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A140" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C140" s="7" t="s">
         <v>601</v>
@@ -3792,10 +4019,10 @@
     </row>
     <row r="141" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A141" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C141" s="7" t="s">
         <v>601</v>
@@ -3803,10 +4030,10 @@
     </row>
     <row r="142" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A142" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C142" s="7" t="s">
         <v>601</v>
@@ -3814,10 +4041,10 @@
     </row>
     <row r="143" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A143" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C143" s="7" t="s">
         <v>601</v>
@@ -3825,10 +4052,10 @@
     </row>
     <row r="144" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A144" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C144" s="7" t="s">
         <v>601</v>
@@ -3836,10 +4063,10 @@
     </row>
     <row r="145" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A145" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C145" s="7" t="s">
         <v>601</v>
@@ -3847,10 +4074,10 @@
     </row>
     <row r="146" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A146" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C146" s="7" t="s">
         <v>601</v>
@@ -3858,10 +4085,10 @@
     </row>
     <row r="147" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A147" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C147" s="7" t="s">
         <v>601</v>
@@ -3869,10 +4096,10 @@
     </row>
     <row r="148" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A148" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C148" s="7" t="s">
         <v>601</v>
@@ -3880,10 +4107,10 @@
     </row>
     <row r="149" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A149" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C149" s="7" t="s">
         <v>601</v>
@@ -3891,10 +4118,10 @@
     </row>
     <row r="150" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A150" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C150" s="7" t="s">
         <v>601</v>
@@ -3902,10 +4129,10 @@
     </row>
     <row r="151" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A151" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C151" s="7" t="s">
         <v>601</v>
@@ -3913,10 +4140,10 @@
     </row>
     <row r="152" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A152" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C152" s="7" t="s">
         <v>601</v>
@@ -3924,10 +4151,10 @@
     </row>
     <row r="153" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A153" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C153" s="7" t="s">
         <v>601</v>
@@ -3935,10 +4162,10 @@
     </row>
     <row r="154" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A154" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C154" s="7" t="s">
         <v>601</v>
@@ -3946,10 +4173,10 @@
     </row>
     <row r="155" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A155" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C155" s="7" t="s">
         <v>601</v>
@@ -3957,10 +4184,10 @@
     </row>
     <row r="156" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A156" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C156" s="7" t="s">
         <v>601</v>
@@ -3968,10 +4195,10 @@
     </row>
     <row r="157" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A157" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C157" s="7" t="s">
         <v>601</v>
@@ -3979,10 +4206,10 @@
     </row>
     <row r="158" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A158" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C158" s="7" t="s">
         <v>601</v>
@@ -3990,10 +4217,10 @@
     </row>
     <row r="159" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A159" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C159" s="7" t="s">
         <v>601</v>
@@ -4001,10 +4228,10 @@
     </row>
     <row r="160" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A160" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C160" s="7" t="s">
         <v>601</v>
@@ -4012,10 +4239,10 @@
     </row>
     <row r="161" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A161" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C161" s="7" t="s">
         <v>601</v>
@@ -4023,10 +4250,10 @@
     </row>
     <row r="162" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A162" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C162" s="7" t="s">
         <v>601</v>
@@ -4034,10 +4261,10 @@
     </row>
     <row r="163" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A163" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C163" s="7" t="s">
         <v>601</v>
@@ -4045,10 +4272,10 @@
     </row>
     <row r="164" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A164" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C164" s="7" t="s">
         <v>601</v>
@@ -4056,10 +4283,10 @@
     </row>
     <row r="165" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A165" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C165" s="7" t="s">
         <v>601</v>
@@ -4067,10 +4294,10 @@
     </row>
     <row r="166" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A166" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C166" s="7" t="s">
         <v>601</v>
@@ -4078,10 +4305,10 @@
     </row>
     <row r="167" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A167" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C167" s="7" t="s">
         <v>601</v>
@@ -4089,10 +4316,10 @@
     </row>
     <row r="168" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A168" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C168" s="7" t="s">
         <v>601</v>
@@ -4100,10 +4327,10 @@
     </row>
     <row r="169" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A169" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C169" s="7" t="s">
         <v>601</v>
@@ -4111,10 +4338,10 @@
     </row>
     <row r="170" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A170" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C170" s="7" t="s">
         <v>601</v>
@@ -4122,10 +4349,10 @@
     </row>
     <row r="171" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A171" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C171" s="7" t="s">
         <v>601</v>
@@ -4133,10 +4360,10 @@
     </row>
     <row r="172" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A172" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C172" s="7" t="s">
         <v>601</v>
@@ -4144,10 +4371,10 @@
     </row>
     <row r="173" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A173" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C173" s="7" t="s">
         <v>601</v>
@@ -4155,10 +4382,10 @@
     </row>
     <row r="174" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A174" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C174" s="7" t="s">
         <v>601</v>
@@ -4166,10 +4393,10 @@
     </row>
     <row r="175" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A175" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C175" s="7" t="s">
         <v>601</v>
@@ -4177,10 +4404,10 @@
     </row>
     <row r="176" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A176" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C176" s="7" t="s">
         <v>601</v>
@@ -4188,10 +4415,10 @@
     </row>
     <row r="177" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A177" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C177" s="7" t="s">
         <v>601</v>
@@ -4199,10 +4426,10 @@
     </row>
     <row r="178" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A178" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C178" s="7" t="s">
         <v>601</v>
@@ -4210,10 +4437,10 @@
     </row>
     <row r="179" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A179" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C179" s="7" t="s">
         <v>601</v>
@@ -4221,10 +4448,10 @@
     </row>
     <row r="180" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A180" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C180" s="7" t="s">
         <v>601</v>
@@ -4232,10 +4459,10 @@
     </row>
     <row r="181" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A181" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C181" s="7" t="s">
         <v>601</v>
@@ -4243,10 +4470,10 @@
     </row>
     <row r="182" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A182" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C182" s="7" t="s">
         <v>601</v>
@@ -4254,10 +4481,10 @@
     </row>
     <row r="183" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A183" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C183" s="7" t="s">
         <v>601</v>
@@ -4265,10 +4492,10 @@
     </row>
     <row r="184" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A184" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C184" s="7" t="s">
         <v>601</v>
@@ -4276,10 +4503,10 @@
     </row>
     <row r="185" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A185" s="7" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="C185" s="7" t="s">
         <v>601</v>
@@ -4287,10 +4514,10 @@
     </row>
     <row r="186" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A186" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C186" s="7" t="s">
         <v>601</v>
@@ -4298,10 +4525,10 @@
     </row>
     <row r="187" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A187" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C187" s="7" t="s">
         <v>601</v>
@@ -4309,10 +4536,10 @@
     </row>
     <row r="188" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A188" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C188" s="7" t="s">
         <v>601</v>
@@ -4320,10 +4547,10 @@
     </row>
     <row r="189" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A189" s="7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C189" s="7" t="s">
         <v>601</v>
@@ -4331,10 +4558,10 @@
     </row>
     <row r="190" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A190" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C190" s="7" t="s">
         <v>601</v>
@@ -4342,10 +4569,10 @@
     </row>
     <row r="191" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A191" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C191" s="7" t="s">
         <v>601</v>
@@ -4353,10 +4580,10 @@
     </row>
     <row r="192" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A192" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C192" s="7" t="s">
         <v>601</v>
@@ -4364,10 +4591,10 @@
     </row>
     <row r="193" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A193" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C193" s="7" t="s">
         <v>601</v>
@@ -4375,10 +4602,10 @@
     </row>
     <row r="194" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A194" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C194" s="7" t="s">
         <v>601</v>
@@ -4386,10 +4613,10 @@
     </row>
     <row r="195" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A195" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C195" s="7" t="s">
         <v>601</v>
@@ -4397,10 +4624,10 @@
     </row>
     <row r="196" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A196" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C196" s="7" t="s">
         <v>601</v>
@@ -4408,10 +4635,10 @@
     </row>
     <row r="197" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A197" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C197" s="7" t="s">
         <v>601</v>
@@ -4419,10 +4646,10 @@
     </row>
     <row r="198" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A198" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C198" s="7" t="s">
         <v>601</v>
@@ -4430,10 +4657,10 @@
     </row>
     <row r="199" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A199" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C199" s="7" t="s">
         <v>601</v>
@@ -4441,10 +4668,10 @@
     </row>
     <row r="200" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A200" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C200" s="7" t="s">
         <v>601</v>
@@ -4452,10 +4679,10 @@
     </row>
     <row r="201" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A201" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C201" s="7" t="s">
         <v>601</v>
@@ -4463,10 +4690,10 @@
     </row>
     <row r="202" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A202" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C202" s="7" t="s">
         <v>601</v>
@@ -4474,10 +4701,10 @@
     </row>
     <row r="203" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A203" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C203" s="7" t="s">
         <v>601</v>
@@ -4485,10 +4712,10 @@
     </row>
     <row r="204" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A204" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C204" s="7" t="s">
         <v>601</v>
@@ -4496,10 +4723,10 @@
     </row>
     <row r="205" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A205" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C205" s="7" t="s">
         <v>601</v>
@@ -4507,10 +4734,10 @@
     </row>
     <row r="206" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A206" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C206" s="7" t="s">
         <v>601</v>
@@ -4518,10 +4745,10 @@
     </row>
     <row r="207" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A207" s="7" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C207" s="7" t="s">
         <v>601</v>
@@ -4529,10 +4756,10 @@
     </row>
     <row r="208" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A208" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C208" s="7" t="s">
         <v>601</v>
@@ -4540,10 +4767,10 @@
     </row>
     <row r="209" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A209" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C209" s="7" t="s">
         <v>601</v>
@@ -4551,10 +4778,10 @@
     </row>
     <row r="210" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A210" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C210" s="7" t="s">
         <v>601</v>
@@ -4562,10 +4789,10 @@
     </row>
     <row r="211" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A211" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C211" s="7" t="s">
         <v>601</v>
@@ -4573,10 +4800,10 @@
     </row>
     <row r="212" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A212" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C212" s="7" t="s">
         <v>601</v>
@@ -4584,10 +4811,10 @@
     </row>
     <row r="213" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A213" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C213" s="7" t="s">
         <v>601</v>
@@ -4595,10 +4822,10 @@
     </row>
     <row r="214" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A214" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C214" s="7" t="s">
         <v>601</v>
@@ -4606,10 +4833,10 @@
     </row>
     <row r="215" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A215" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B215" s="7" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C215" s="7" t="s">
         <v>601</v>
@@ -4617,10 +4844,10 @@
     </row>
     <row r="216" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A216" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C216" s="7" t="s">
         <v>601</v>
@@ -4628,10 +4855,10 @@
     </row>
     <row r="217" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A217" s="7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C217" s="7" t="s">
         <v>601</v>
@@ -4639,10 +4866,10 @@
     </row>
     <row r="218" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A218" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C218" s="7" t="s">
         <v>601</v>
@@ -4650,10 +4877,10 @@
     </row>
     <row r="219" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A219" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C219" s="7" t="s">
         <v>601</v>
@@ -4661,10 +4888,10 @@
     </row>
     <row r="220" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A220" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C220" s="7" t="s">
         <v>601</v>
@@ -4672,10 +4899,10 @@
     </row>
     <row r="221" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A221" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C221" s="7" t="s">
         <v>601</v>
@@ -4683,10 +4910,10 @@
     </row>
     <row r="222" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A222" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B222" s="7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C222" s="7" t="s">
         <v>601</v>
@@ -4694,10 +4921,10 @@
     </row>
     <row r="223" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A223" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B223" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C223" s="7" t="s">
         <v>601</v>
@@ -4705,10 +4932,10 @@
     </row>
     <row r="224" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A224" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B224" s="7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C224" s="7" t="s">
         <v>601</v>
@@ -4716,10 +4943,10 @@
     </row>
     <row r="225" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A225" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C225" s="7" t="s">
         <v>601</v>
@@ -4727,10 +4954,10 @@
     </row>
     <row r="226" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A226" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C226" s="7" t="s">
         <v>601</v>
@@ -4738,10 +4965,10 @@
     </row>
     <row r="227" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A227" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C227" s="7" t="s">
         <v>601</v>
@@ -4749,10 +4976,10 @@
     </row>
     <row r="228" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A228" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B228" s="7" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C228" s="7" t="s">
         <v>601</v>
@@ -4760,10 +4987,10 @@
     </row>
     <row r="229" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A229" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B229" s="7" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C229" s="7" t="s">
         <v>601</v>
@@ -4771,10 +4998,10 @@
     </row>
     <row r="230" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A230" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B230" s="7" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C230" s="7" t="s">
         <v>601</v>
@@ -4782,10 +5009,10 @@
     </row>
     <row r="231" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A231" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B231" s="7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C231" s="7" t="s">
         <v>601</v>
@@ -4793,10 +5020,10 @@
     </row>
     <row r="232" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A232" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B232" s="7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C232" s="7" t="s">
         <v>601</v>
@@ -4804,10 +5031,10 @@
     </row>
     <row r="233" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A233" s="7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B233" s="7" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C233" s="7" t="s">
         <v>601</v>
@@ -4815,10 +5042,10 @@
     </row>
     <row r="234" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A234" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B234" s="7" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C234" s="7" t="s">
         <v>601</v>
@@ -4826,10 +5053,10 @@
     </row>
     <row r="235" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A235" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B235" s="7" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C235" s="7" t="s">
         <v>601</v>
@@ -4837,10 +5064,10 @@
     </row>
     <row r="236" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A236" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B236" s="7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C236" s="7" t="s">
         <v>601</v>
@@ -4848,10 +5075,10 @@
     </row>
     <row r="237" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A237" s="7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B237" s="7" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C237" s="7" t="s">
         <v>601</v>
@@ -4859,10 +5086,10 @@
     </row>
     <row r="238" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A238" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B238" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C238" s="7" t="s">
         <v>601</v>
@@ -4870,10 +5097,10 @@
     </row>
     <row r="239" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A239" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B239" s="7" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C239" s="7" t="s">
         <v>601</v>
@@ -4881,10 +5108,10 @@
     </row>
     <row r="240" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A240" s="7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B240" s="7" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C240" s="7" t="s">
         <v>601</v>
@@ -4892,10 +5119,10 @@
     </row>
     <row r="241" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A241" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B241" s="7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C241" s="7" t="s">
         <v>601</v>
@@ -4903,10 +5130,10 @@
     </row>
     <row r="242" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A242" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C242" s="7" t="s">
         <v>601</v>
@@ -4914,10 +5141,10 @@
     </row>
     <row r="243" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A243" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B243" s="7" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C243" s="7" t="s">
         <v>601</v>
@@ -4925,10 +5152,10 @@
     </row>
     <row r="244" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A244" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B244" s="7" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C244" s="7" t="s">
         <v>601</v>
@@ -4936,10 +5163,10 @@
     </row>
     <row r="245" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A245" s="7" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B245" s="7" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C245" s="7" t="s">
         <v>601</v>
@@ -4947,10 +5174,10 @@
     </row>
     <row r="246" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A246" s="7" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C246" s="7" t="s">
         <v>601</v>
@@ -4958,10 +5185,10 @@
     </row>
     <row r="247" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A247" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B247" s="7" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C247" s="7" t="s">
         <v>601</v>
@@ -4969,10 +5196,10 @@
     </row>
     <row r="248" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A248" s="7" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B248" s="7" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C248" s="7" t="s">
         <v>601</v>
@@ -4980,10 +5207,10 @@
     </row>
     <row r="249" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A249" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B249" s="7" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C249" s="7" t="s">
         <v>601</v>
@@ -4991,10 +5218,10 @@
     </row>
     <row r="250" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A250" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B250" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C250" s="7" t="s">
         <v>601</v>
@@ -5002,10 +5229,10 @@
     </row>
     <row r="251" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A251" s="7" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B251" s="7" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C251" s="7" t="s">
         <v>601</v>
@@ -5013,10 +5240,10 @@
     </row>
     <row r="252" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A252" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B252" s="7" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C252" s="7" t="s">
         <v>601</v>
@@ -5024,10 +5251,10 @@
     </row>
     <row r="253" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A253" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B253" s="7" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C253" s="7" t="s">
         <v>601</v>
@@ -5035,10 +5262,10 @@
     </row>
     <row r="254" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A254" s="7" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B254" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C254" s="7" t="s">
         <v>601</v>
@@ -5046,10 +5273,10 @@
     </row>
     <row r="255" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A255" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B255" s="7" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C255" s="7" t="s">
         <v>601</v>
@@ -5057,10 +5284,10 @@
     </row>
     <row r="256" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A256" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B256" s="7" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C256" s="7" t="s">
         <v>601</v>
@@ -5068,10 +5295,10 @@
     </row>
     <row r="257" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A257" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B257" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C257" s="7" t="s">
         <v>601</v>
@@ -5079,10 +5306,10 @@
     </row>
     <row r="258" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A258" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B258" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C258" s="7" t="s">
         <v>601</v>
@@ -5090,10 +5317,10 @@
     </row>
     <row r="259" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A259" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B259" s="7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C259" s="7" t="s">
         <v>601</v>
@@ -5101,10 +5328,10 @@
     </row>
     <row r="260" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A260" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B260" s="7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C260" s="7" t="s">
         <v>601</v>
@@ -5112,10 +5339,10 @@
     </row>
     <row r="261" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A261" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B261" s="7" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C261" s="7" t="s">
         <v>601</v>
@@ -5123,10 +5350,10 @@
     </row>
     <row r="262" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A262" s="7" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B262" s="7" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C262" s="7" t="s">
         <v>601</v>
@@ -5134,10 +5361,10 @@
     </row>
     <row r="263" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A263" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B263" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C263" s="7" t="s">
         <v>601</v>
@@ -5145,10 +5372,10 @@
     </row>
     <row r="264" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A264" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B264" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C264" s="7" t="s">
         <v>601</v>
@@ -5156,10 +5383,10 @@
     </row>
     <row r="265" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A265" s="7" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B265" s="7" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C265" s="7" t="s">
         <v>601</v>
@@ -5167,10 +5394,10 @@
     </row>
     <row r="266" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A266" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B266" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C266" s="7" t="s">
         <v>601</v>
@@ -5178,10 +5405,10 @@
     </row>
     <row r="267" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A267" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B267" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C267" s="7" t="s">
         <v>601</v>
@@ -5189,10 +5416,10 @@
     </row>
     <row r="268" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A268" s="7" t="s">
-        <v>57</v>
+        <v>241</v>
       </c>
       <c r="B268" s="7" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C268" s="7" t="s">
         <v>601</v>
@@ -5200,10 +5427,10 @@
     </row>
     <row r="269" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A269" s="7" t="s">
-        <v>243</v>
+        <v>57</v>
       </c>
       <c r="B269" s="7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C269" s="7" t="s">
         <v>601</v>
@@ -5211,10 +5438,10 @@
     </row>
     <row r="270" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A270" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B270" s="7" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C270" s="7" t="s">
         <v>601</v>
@@ -5222,10 +5449,10 @@
     </row>
     <row r="271" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A271" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B271" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C271" s="7" t="s">
         <v>601</v>
@@ -5233,10 +5460,10 @@
     </row>
     <row r="272" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A272" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B272" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C272" s="7" t="s">
         <v>601</v>
@@ -5244,10 +5471,10 @@
     </row>
     <row r="273" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A273" s="7" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B273" s="7" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="C273" s="7" t="s">
         <v>601</v>
@@ -5255,10 +5482,10 @@
     </row>
     <row r="274" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A274" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B274" s="7" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C274" s="7" t="s">
         <v>601</v>
@@ -5266,10 +5493,10 @@
     </row>
     <row r="275" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A275" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B275" s="7" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C275" s="7" t="s">
         <v>601</v>
@@ -5277,10 +5504,10 @@
     </row>
     <row r="276" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A276" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B276" s="7" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C276" s="7" t="s">
         <v>601</v>
@@ -5288,10 +5515,10 @@
     </row>
     <row r="277" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A277" s="7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B277" s="7" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C277" s="7" t="s">
         <v>601</v>
@@ -5299,10 +5526,10 @@
     </row>
     <row r="278" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A278" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B278" s="7" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C278" s="7" t="s">
         <v>601</v>
@@ -5310,10 +5537,10 @@
     </row>
     <row r="279" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A279" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B279" s="7" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C279" s="7" t="s">
         <v>601</v>
@@ -5321,10 +5548,10 @@
     </row>
     <row r="280" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A280" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B280" s="7" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C280" s="7" t="s">
         <v>601</v>
@@ -5332,10 +5559,10 @@
     </row>
     <row r="281" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A281" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B281" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C281" s="7" t="s">
         <v>601</v>
@@ -5343,10 +5570,10 @@
     </row>
     <row r="282" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A282" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B282" s="7" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C282" s="7" t="s">
         <v>601</v>
@@ -5354,10 +5581,10 @@
     </row>
     <row r="283" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A283" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B283" s="7" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C283" s="7" t="s">
         <v>601</v>
@@ -5365,10 +5592,10 @@
     </row>
     <row r="284" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A284" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B284" s="7" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C284" s="7" t="s">
         <v>601</v>
@@ -5376,10 +5603,10 @@
     </row>
     <row r="285" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A285" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B285" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C285" s="7" t="s">
         <v>601</v>
@@ -5387,10 +5614,10 @@
     </row>
     <row r="286" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A286" s="7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B286" s="7" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C286" s="7" t="s">
         <v>601</v>
@@ -5398,10 +5625,10 @@
     </row>
     <row r="287" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A287" s="7" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B287" s="7" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="C287" s="7" t="s">
         <v>601</v>
@@ -5409,10 +5636,10 @@
     </row>
     <row r="288" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A288" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B288" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C288" s="7" t="s">
         <v>601</v>
@@ -5420,10 +5647,10 @@
     </row>
     <row r="289" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A289" s="7" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B289" s="7" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C289" s="7" t="s">
         <v>601</v>
@@ -5431,10 +5658,10 @@
     </row>
     <row r="290" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A290" s="7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B290" s="7" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C290" s="7" t="s">
         <v>601</v>
@@ -5442,10 +5669,10 @@
     </row>
     <row r="291" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A291" s="7" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B291" s="7" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C291" s="7" t="s">
         <v>601</v>
@@ -5453,10 +5680,10 @@
     </row>
     <row r="292" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A292" s="7" t="s">
-        <v>236</v>
+        <v>284</v>
       </c>
       <c r="B292" s="7" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C292" s="7" t="s">
         <v>601</v>
@@ -5464,10 +5691,10 @@
     </row>
     <row r="293" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A293" s="7" t="s">
-        <v>287</v>
+        <v>236</v>
       </c>
       <c r="B293" s="7" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C293" s="7" t="s">
         <v>601</v>
@@ -5475,10 +5702,10 @@
     </row>
     <row r="294" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A294" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B294" s="7" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C294" s="7" t="s">
         <v>601</v>
@@ -5486,10 +5713,10 @@
     </row>
     <row r="295" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A295" s="7" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B295" s="7" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C295" s="7" t="s">
         <v>601</v>
@@ -5497,10 +5724,10 @@
     </row>
     <row r="296" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A296" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B296" s="7" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C296" s="7" t="s">
         <v>601</v>
@@ -5508,10 +5735,10 @@
     </row>
     <row r="297" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A297" s="7" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B297" s="7" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C297" s="7" t="s">
         <v>601</v>
@@ -5519,10 +5746,10 @@
     </row>
     <row r="298" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A298" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B298" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C298" s="7" t="s">
         <v>601</v>
@@ -5530,10 +5757,10 @@
     </row>
     <row r="299" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A299" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B299" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C299" s="7" t="s">
         <v>601</v>
@@ -5541,10 +5768,10 @@
     </row>
     <row r="300" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A300" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B300" s="7" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C300" s="7" t="s">
         <v>601</v>
@@ -5552,21 +5779,440 @@
     </row>
     <row r="301" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A301" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="B301" s="7" t="s">
+        <v>594</v>
+      </c>
+      <c r="C301" s="7" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A302" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="B301" s="7" t="s">
+      <c r="B302" s="7" t="s">
         <v>596</v>
       </c>
-      <c r="C301" s="7" t="s">
+      <c r="C302" s="7" t="s">
         <v>601</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="C1:C301" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C301">
-      <sortCondition ref="C1:C301"/>
+  <autoFilter ref="C1:C302" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C302">
+      <sortCondition ref="C1:C302"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25AAEC17-1E37-A540-8EE1-63B0993F5F72}">
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="76" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2" t="s">
+        <v>608</v>
+      </c>
+      <c r="C2" t="s">
+        <v>609</v>
+      </c>
+      <c r="D2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>611</v>
+      </c>
+      <c r="B3" t="s">
+        <v>612</v>
+      </c>
+      <c r="C3" t="s">
+        <v>613</v>
+      </c>
+      <c r="D3" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>615</v>
+      </c>
+      <c r="B4" t="s">
+        <v>616</v>
+      </c>
+      <c r="C4" t="s">
+        <v>617</v>
+      </c>
+      <c r="D4" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>619</v>
+      </c>
+      <c r="B5" t="s">
+        <v>616</v>
+      </c>
+      <c r="C5" t="s">
+        <v>617</v>
+      </c>
+      <c r="D5" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>621</v>
+      </c>
+      <c r="B6" t="s">
+        <v>616</v>
+      </c>
+      <c r="C6" t="s">
+        <v>622</v>
+      </c>
+      <c r="D6" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>624</v>
+      </c>
+      <c r="B7" t="s">
+        <v>616</v>
+      </c>
+      <c r="C7" t="s">
+        <v>625</v>
+      </c>
+      <c r="D7" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>627</v>
+      </c>
+      <c r="B8" t="s">
+        <v>616</v>
+      </c>
+      <c r="C8" t="s">
+        <v>628</v>
+      </c>
+      <c r="D8" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>630</v>
+      </c>
+      <c r="B9" t="s">
+        <v>616</v>
+      </c>
+      <c r="C9" t="s">
+        <v>628</v>
+      </c>
+      <c r="D9" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>632</v>
+      </c>
+      <c r="B10" t="s">
+        <v>616</v>
+      </c>
+      <c r="C10" t="s">
+        <v>628</v>
+      </c>
+      <c r="D10" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>634</v>
+      </c>
+      <c r="B11" t="s">
+        <v>616</v>
+      </c>
+      <c r="C11" t="s">
+        <v>628</v>
+      </c>
+      <c r="D11" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>636</v>
+      </c>
+      <c r="B12" t="s">
+        <v>616</v>
+      </c>
+      <c r="C12" t="s">
+        <v>628</v>
+      </c>
+      <c r="D12" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>638</v>
+      </c>
+      <c r="B13" t="s">
+        <v>616</v>
+      </c>
+      <c r="C13" t="s">
+        <v>628</v>
+      </c>
+      <c r="D13" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>640</v>
+      </c>
+      <c r="B14" t="s">
+        <v>616</v>
+      </c>
+      <c r="C14" t="s">
+        <v>628</v>
+      </c>
+      <c r="D14" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>642</v>
+      </c>
+      <c r="B15" t="s">
+        <v>616</v>
+      </c>
+      <c r="C15" t="s">
+        <v>628</v>
+      </c>
+      <c r="D15" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>644</v>
+      </c>
+      <c r="B16" t="s">
+        <v>616</v>
+      </c>
+      <c r="C16" t="s">
+        <v>628</v>
+      </c>
+      <c r="D16" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>646</v>
+      </c>
+      <c r="B17" t="s">
+        <v>616</v>
+      </c>
+      <c r="C17" t="s">
+        <v>647</v>
+      </c>
+      <c r="D17" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>649</v>
+      </c>
+      <c r="B18" t="s">
+        <v>650</v>
+      </c>
+      <c r="C18" t="s">
+        <v>651</v>
+      </c>
+      <c r="D18" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>653</v>
+      </c>
+      <c r="B19" t="s">
+        <v>616</v>
+      </c>
+      <c r="C19" t="s">
+        <v>617</v>
+      </c>
+      <c r="D19" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>655</v>
+      </c>
+      <c r="B20" t="s">
+        <v>616</v>
+      </c>
+      <c r="C20" t="s">
+        <v>617</v>
+      </c>
+      <c r="D20" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>657</v>
+      </c>
+      <c r="B21" t="s">
+        <v>616</v>
+      </c>
+      <c r="C21" t="s">
+        <v>617</v>
+      </c>
+      <c r="D21" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>659</v>
+      </c>
+      <c r="B22" t="s">
+        <v>616</v>
+      </c>
+      <c r="C22" t="s">
+        <v>617</v>
+      </c>
+      <c r="D22" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>661</v>
+      </c>
+      <c r="B23" t="s">
+        <v>616</v>
+      </c>
+      <c r="C23" t="s">
+        <v>617</v>
+      </c>
+      <c r="D23" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>663</v>
+      </c>
+      <c r="B24" t="s">
+        <v>616</v>
+      </c>
+      <c r="C24" t="s">
+        <v>617</v>
+      </c>
+      <c r="D24" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>665</v>
+      </c>
+      <c r="B25" t="s">
+        <v>616</v>
+      </c>
+      <c r="C25" t="s">
+        <v>617</v>
+      </c>
+      <c r="D25" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>667</v>
+      </c>
+      <c r="B26" t="s">
+        <v>616</v>
+      </c>
+      <c r="C26" t="s">
+        <v>617</v>
+      </c>
+      <c r="D26" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>669</v>
+      </c>
+      <c r="B27" t="s">
+        <v>616</v>
+      </c>
+      <c r="C27" t="s">
+        <v>670</v>
+      </c>
+      <c r="D27" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>672</v>
+      </c>
+      <c r="B28" t="s">
+        <v>650</v>
+      </c>
+      <c r="C28" t="s">
+        <v>673</v>
+      </c>
+      <c r="D28" t="s">
+        <v>674</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>